--- a/S2 CP/ClinicalExam/CE_CP_T1.xlsx
+++ b/S2 CP/ClinicalExam/CE_CP_T1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GBW_MyPrograms\PredSim-workshop-smalll-2025\S2 CP\ClinicalExam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GBW_MyPrograms\PredSim-workshop-ESMAC-2026\S2 CP\ClinicalExam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA7EE49-B3D5-419A-9854-9331E7603DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19376F35-79BF-4F1D-B054-2786AE51B787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -48,9 +48,6 @@
     <t>pROM_Ankledf90_L</t>
   </si>
   <si>
-    <t>CP_SMALLL</t>
-  </si>
-  <si>
     <t>pROM_Poplbi_R</t>
   </si>
   <si>
@@ -130,6 +127,9 @@
   </si>
   <si>
     <t>Step 6</t>
+  </si>
+  <si>
+    <t>CP_ESMAC</t>
   </si>
 </sst>
 </file>
@@ -547,10 +547,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -562,7 +562,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="5"/>
@@ -571,13 +571,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="14">
         <v>3</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="5"/>
@@ -586,7 +586,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="14">
         <v>3</v>
@@ -598,7 +598,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="14">
         <v>5</v>
@@ -610,7 +610,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="14">
         <v>5</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="14">
         <v>3</v>
@@ -634,7 +634,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="14">
         <v>3</v>
@@ -646,7 +646,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="14">
         <v>4</v>
@@ -658,7 +658,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="14">
         <v>5</v>
@@ -668,7 +668,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="14">
         <v>3</v>
@@ -678,7 +678,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="14">
         <v>4</v>
@@ -686,7 +686,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="14">
         <v>3</v>
@@ -694,7 +694,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="14">
         <v>3</v>
@@ -706,14 +706,14 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" s="14">
         <v>-70</v>
@@ -729,7 +729,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" s="14">
         <v>-80</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B21" s="14">
         <v>-65</v>
@@ -745,7 +745,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" s="14">
         <v>15</v>
@@ -753,7 +753,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" s="14">
         <v>10</v>
@@ -783,7 +783,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" s="12"/>
       <c r="E26" s="1"/>
@@ -791,7 +791,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B27" s="3">
         <v>0</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B28" s="3">
         <v>0</v>
@@ -811,20 +811,20 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="5"/>
